--- a/rag_eval_comparison.xlsx
+++ b/rag_eval_comparison.xlsx
@@ -88,12 +88,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -143,16 +143,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,19 +161,22 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I6"/>
+  <dimension ref="B1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -550,13 +553,14 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>📊  NIFTY RAG Chatbot — Model Comparison</t>
+          <t>NIFTY RAG Chatbot - Model Comparison</t>
         </is>
       </c>
     </row>
@@ -569,25 +573,25 @@
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Avg Score
-(1–5)</t>
+(1-5)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Faithfulness
-(1–5)</t>
+(1-5)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Answer Relevance
-(1–5)</t>
+(1-5)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Completeness
-(1–5)</t>
+(1-5)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -598,11 +602,17 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Anchor Hit
+          <t>Context Hit
 Rate %</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Answer Mentions
+Entity %</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Error Rate
 %</t>
@@ -616,58 +626,68 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>26.3%</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>4.8%</t>
+        <v>3</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>33.36</v>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>90.5%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>openai/gpt-oss</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
-        <v>2.98</v>
+      <c r="C5" s="4" t="n">
+        <v>3.27</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2.43</v>
+        <v>2.71</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>3.19</v>
+        <v>3.48</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>2.24</v>
+        <v>3.27</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
+          <t>94.7%</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
           <t>15.8%</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -680,26 +700,31 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3.57</v>
+        <v>3.67</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+        <v>2.81</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>94.7%</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>52.6%</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -707,7 +732,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -719,21 +744,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -759,43 +787,60 @@
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
+          <t>Retrieved Context</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
           <t>Faithfulness
-(1–5)</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
+(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Answer Relevance
-(1–5)</t>
-        </is>
-      </c>
-      <c r="G1" s="11" t="inlineStr">
+(1-5)</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Completeness
-(1–5)</t>
-        </is>
-      </c>
-      <c r="H1" s="11" t="inlineStr">
+(1-5)</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Avg Score</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
-        <is>
-          <t>Anchor Hit</t>
-        </is>
-      </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
+          <t>Context Hit</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>Answer Mentions
+Entity</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>All Entities
+Hit</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
           <t>Latency (s)</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Judge Reasoning</t>
         </is>
@@ -817,83 +862,89 @@
           <t>What is the current revenue of TCS?</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records. However, for the most recent reporting period ending March 31, 2026, TCS reported an EBITDA of ₹200.33 Billion, Gross Profit of ₹291.11 Billion, and Net Income of ₹137.18 Billion.</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="K2" s="12" t="inlineStr"/>
+      <c r="D2" s="12" t="inlineStr"/>
+      <c r="E2" s="12" t="inlineStr"/>
+      <c r="F2" s="13" t="n"/>
+      <c r="G2" s="13" t="n"/>
+      <c r="H2" s="13" t="n"/>
+      <c r="I2" s="13" t="n"/>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>Provides some relevant data but lacks current revenue</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199083, Requested 1200. Please try again in 2m2.256s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O2" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Single-Company Factual</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Who leads Reliance Industries?</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records. The provided context mentions Mukesh Ambani specifying at the 2022 RIL AGM that his son Anant Ambani will take over the new energy business, but it does not explicitly identify the current overall leader of Reliance Industries.</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="n">
-        <v>5.025</v>
-      </c>
-      <c r="K3" s="16" t="inlineStr"/>
-      <c r="L3" s="16" t="inlineStr">
-        <is>
-          <t>Answer avoids hallucinations but lacks explicit leader</t>
+      <c r="D3" s="13" t="inlineStr"/>
+      <c r="E3" s="13" t="inlineStr"/>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="13" t="n"/>
+      <c r="H3" s="13" t="n"/>
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="13" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199057, Requested 1277. Please try again in 2m24.288s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O3" s="15" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -913,83 +964,89 @@
           <t>What sector does Infosys operate in?</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Based on the provided records, Infosys operates in the **Technology** sector.</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>2.435</v>
-      </c>
-      <c r="K4" s="12" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr"/>
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>Answer is based on provided records and question</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199029, Requested 1263. Please try again in 2m6.143999999s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Single-Company Factual</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>What is HDFC Bank's net profit for the latest reported quarter?</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>Based on the provided records, HDFC Bank's net profit (Net Income) for the latest reported quarter ending June 30, 2025, is ₹162.58 Bn.</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>4.599</v>
-      </c>
-      <c r="K5" s="16" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr">
-        <is>
-          <t>Grounded in facts, but lacks date range</t>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199001, Requested 1777. Please try again in 5m36.096s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O5" s="15" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -1009,83 +1066,89 @@
           <t>What is the debt-to-equity ratio of Tata Motors?</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>3.147</v>
-      </c>
-      <c r="K6" s="12" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr"/>
+      <c r="E6" s="12" t="inlineStr"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>Answer avoids hallucinations but lacks data</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 198975, Requested 2655. Please try again in 11m44.16s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O6" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Comparison</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Compare the revenue of TCS and Infosys.</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="n">
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per minute (TPM): Limit 8000, Used 4474, Requested 3841. Please try again in 2.3625s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>Failed to provide factual answer</t>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 198948, Requested 1794. Please try again in 5m20.544s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O7" s="15" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -1105,87 +1168,89 @@
           <t>Which has a higher market cap, Wipro or HCL Technologies?</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>2.226</v>
-      </c>
-      <c r="K8" s="12" t="inlineStr"/>
+      <c r="D8" s="12" t="inlineStr"/>
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>Answer avoids facts, not relevant to question</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 198921, Requested 2130. Please try again in 7m34.032s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>C03</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Comparison</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>How does HDFC Bank's PAT compare to ICICI Bank?</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Based on the most recent data available in the Financial Graph:
-* **HDFC Bank** reported a Net Income of ₹162.58 Billion as of June 30, 2025.
-* **ICICI Bank** reported a Net Income of ₹147.55 Billion as of March 31, 2026.
-Comparing the latest available reporting periods, HDFC Bank's Net Income is higher than ICICI Bank's. 
-Source: Financial Graph</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="K9" s="16" t="inlineStr"/>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>Grounded in facts, but lacks specific date range</t>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 198894, Requested 2229. Please try again in 8m5.136s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O9" s="15" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -1210,78 +1275,101 @@
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="12">
+        <f>== BEL | Company | Bharat Electronics Limited ===
+Sector: Industrials
+Industry: Aerospace &amp; Defense
+Insiders Holding: 53.2%
+Institutions Holding: 25.6%
+EBITDA: ₹22.66 Billion (2025-12-31) | ₹14.02 Billion (2025-06-30) | ₹31.52 Billion (2025-03-31) | ₹18.56 Billion (2024-12-31) | ₹15.58 Billion (2024-09-30) | ₹22.66 Billion (2025-12-31) | ₹14.02 Billion (2025-06-30) | ₹30.10 Billion (2025-03-31) | ₹18.56 Billion (2024-12-31) | ₹15.58 Billion (2024-09-30)
+Gross Profit: ₹33.29 Billion (2025-12-31)...</f>
+        <v/>
+      </c>
+      <c r="F10" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>2.827</v>
-      </c>
-      <c r="K10" s="12" t="inlineStr"/>
+      <c r="G10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>2.476</v>
+      </c>
+      <c r="N10" s="12" t="inlineStr"/>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
           <t>Answer avoids hallucinations but lacks data</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>List all banking companies in the NIFTY 50.</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>Answer lacks factual data but attempts to address question</t>
+      <c r="D11" s="13" t="inlineStr"/>
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199964, Requested 799. Please try again in 5m29.616s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O11" s="15" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -1301,87 +1389,89 @@
           <t>Which energy sector stocks are part of NIFTY 50?</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Based on the provided context, the energy sector stocks are:
-*   Adani Enterprises Limited (ADANIENT)
-*   Coal India Limited (COALINDIA)
-*   Oil and Natural Gas Corporation Limited (ONGC)
-*   Reliance Industries Limited (RELIANCE)</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>7.139</v>
-      </c>
-      <c r="K12" s="12" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr"/>
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>Answer is based on NIFTY 50 data, but lacks specific dates or time frame</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199929, Requested 792. Please try again in 5m11.472s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Financial Metric</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>What is the P/E ratio of Bajaj Finance?</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="n">
-        <v>10.666</v>
-      </c>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>Answer avoids hallucinations but lacks data</t>
+      <c r="D13" s="13" t="inlineStr"/>
+      <c r="E13" s="13" t="inlineStr"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199903, Requested 2271. Please try again in 15m39.168s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O13" s="15" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -1401,83 +1491,89 @@
           <t>What is the EPS of Asian Paints?</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>8.513</v>
-      </c>
-      <c r="K14" s="12" t="inlineStr"/>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>Answer avoids hallucinations but lacks data</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199877, Requested 1931. Please try again in 13m1.055999999s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O14" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Financial Metric</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>What is the dividend yield of Coal India?</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="n">
-        <v>5.669</v>
-      </c>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>Answer avoids hallucinations but lacks data</t>
+      <c r="D15" s="13" t="inlineStr"/>
+      <c r="E15" s="13" t="inlineStr"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="13" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199849, Requested 2079. Please try again in 13m52.896s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O15" s="15" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -1497,83 +1593,89 @@
           <t>Who is the CEO of Wipro?</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>5.861</v>
-      </c>
-      <c r="K16" s="12" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr"/>
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>Answer avoids hallucinations but lacks factual data</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199823, Requested 1243. Please try again in 7m40.511999999s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>P02</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Leadership</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Who leads Maruti Suzuki?</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="n">
-        <v>2.992</v>
-      </c>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>Answer avoids hallucinations but lacks factual data</t>
+      <c r="D17" s="13" t="inlineStr"/>
+      <c r="E17" s="13" t="inlineStr"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199796, Requested 1213. Please try again in 7m15.888s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O17" s="15" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -1593,83 +1695,89 @@
           <t>What percentage of ONGC is held by institutions?</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Institutions hold 22.8% of ONGC.</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>3.072</v>
-      </c>
-      <c r="K18" s="12" t="inlineStr"/>
+      <c r="D18" s="12" t="inlineStr"/>
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>Answer is based on publicly available data</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199770, Requested 2004. Please try again in 12m46.367999999s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>SH02</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Shareholding</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>What is the insider holding percentage for Sun Pharmaceutical?</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="n">
-        <v>6.117</v>
-      </c>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>Does not provide factual data, only indicates lack of information</t>
+      <c r="D19" s="13" t="inlineStr"/>
+      <c r="E19" s="13" t="inlineStr"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199731, Requested 834. Please try again in 4m4.079999999s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O19" s="15" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -1689,81 +1797,108 @@
           <t>What is the current gold price?</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr"/>
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199700, Requested 1388. Please try again in 7m50.016s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Summarise the last 5 years of NIFTY performance.</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>### 1975–1994
+---
+### 1995–2004
+---
+## History
+---
+Community 5 Summary: Based on the provided community subgraph, here is a concise summary of its key themes, relationships, and significance:
+**Key Themes:**
+1. **Utilities Sector Dominance**: The community revolves around the Utilities sector, with NTPC and POWERGRID being prominent companies.
+2. **Insider and Institutional Holdings**: Both insider and institutional holdings are significant in this community, indicating a high level of interes...</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>3.223</v>
-      </c>
-      <c r="K20" s="12" t="inlineStr"/>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>Does not have data in records</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Robustness</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Summarise the last 5 years of NIFTY performance.</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="n">
-        <v>2.174</v>
-      </c>
-      <c r="K21" s="16" t="inlineStr"/>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="G21" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>64.23699999999999</v>
+      </c>
+      <c r="N21" s="13" t="inlineStr"/>
+      <c r="O21" s="15" t="inlineStr">
         <is>
           <t>Avoids data but provides direct answer</t>
         </is>
@@ -1785,123 +1920,38 @@
           <t>Tell me about TCS revenue, then compare it with Infosys revenue.</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>&lt;think&gt;
-Thinking Process:
-1.  **Analyze the Request**:
-    *   Target 1: TCS revenue.
-    *   Target 2: Infosys revenue.
-    *   Action: Compare the two.
-    *   Constraints: Use ONLY provided context. Use '₹' prefix. Format as Cr or Bn. Prioritize most recent date. No thought leakage.
-2.  **Scan Context for TCS Revenue**:
-    *   Look under `=== TCS | Company | Tata Consultancy Services Limited ===`
-    *   Fields available: EBITDA, Gross Profit, Net Income.
-    *   *Wait*, is "Revenue" explicitly listed?
-    *   Let's check the fields:
-        *   EBITDA: ₹200.33 Billion (2026-03-31) ...
-        *   Gross Profit: ₹291.11 Billion (2026-03-31) ...
-        *   Net Income: ₹137.18 Billion (2026-03-31) ...
-    *   There is no explicit "Revenue" field in the provided context for TCS.
-    *   Let's check Infosys context:
-        *   `=== INFY | Company | Infosys Limited ===`
-        *   EBITDA: ₹1.33 Billion (2026-03-31) ...
-        *   Gross Profit: ₹1.55 Billion (2026-03-31) ...
-        *   Net Income: ₹91.90 Crore (2026-03-31) ...
-    *   There is no explicit "Revenue" field for Infosys either.
-3.  **Evaluate Grounding Rules**:
-    *   Rule 1: "Context Only: Use ONLY the provided context. If the answer isn't there, say: 'I do not have that data in my records.'"
-    *   Since "Revenue" is not explicitly provided in the context for either TCS or Infosys (only EBITDA, Gross Profit, and Net Income are listed), I must state that I do not have that data.
-4.  **Formulate Response**:
-    *   State clearly that revenue data is not available in the provided records for either TCS or Infosys.
-    *   (Optional but helpful, strictly adhering to context): Mention the available financial metrics (like Gross Profit or Net Income) if it helps, but the prompt specifically asked for *revenue*. The strict rule says "If the answer isn't there, say: 'I do not have that data in my records.'"
-    *   Let's stick strictly to the rule: "I do not have that data in my records." regarding revenue.
-    *Wait*, let me double-check the context text to ensure I didn't miss "Revenue" hidden in the text.
-    *   TCS text: "In March 2018, Tata Sons sold TCS shares worth $1.25 billion..." No revenue.
-    *   INFY text: Just the financial metrics list. No revenue.
-    *Conclusion*: I cannot answer the question about revenue. I will state: "I do not have that data in my records."
-    *Self-Correction/Refinement*: Sometimes "Gross Profit" or "EBITDA" is mistaken for revenue by users, but as an AI, I must be precise. I will state that revenue data is not available, but I can provide the most recent Gross Profit or Net Income if appropriate, or just stick to the exact phrase required by the prompt.
-    Prompt rule: "If the answer isn't there, say: 'I do not have that data in my records.'"
-    Let's output exactly that.
-    *Wait*, is there any other interpretation? Could "Gross Profit" be considered revenue in this specific truncated dataset? No, Gross Profit is distinct from Revenue. I will state I don't have the revenue data.
-    Let's write: "I do not have that data in my records." regarding the revenue for both TCS and Infosys.
-    Actually, to be more helpful while strictly following the negative constraint:
-    "I do not have that data in my records. The provided context does not contain revenue figures for either TCS or Infosys, though it does list their most recent Gross Profit and Net Income." -&gt; This is better, but the strict rule says "say: 'I do not have that data in my records.'" I will just say that to be safe.
-    Let's just say: "I do not have that data in my records."
-    Wait, what if the user meant "Gross Profit" or "Net Income"? I'll just state the lack of revenue data.
-    Let's review the exact wording of the rule: "If the answer isn't there, say: "I do not have that data in my records.""
-    Final decision: "I do not have that data in my records." (Since revenue is not in the context).
-    *Alternative*: Maybe I should provide the Gross Profit as a proxy? No, that violates "Context Only" and accuracy. Revenue != Gross Profit.
-    I will output: "I do not have that data in my records."
-    Wait, can I provide the Net Income or Gross Profit instead? "I do not have that data in my records. However, I can provide their most recent Gross Profit and Net Income."
-    Let's just provide the exact phrase. "I do not have that data in my records."
-    Actually, looking at the context, there is NO revenue. So the answer is definitively missing.
-    Let's write: "I do not have that data in my records."
-    To be slightly more conversational but compliant: "I do not have that data in my records. The provided context does not list revenue figures for either TCS or Infosys."
-    Let's stick to the simplest compliant answer.
-    "I do not have that data in my records."
-    (End of thought process)
-    Wait! Is it possible the prompt implies using Gross Profit as revenue? No.
-    I will just say "I do not have that data in my records."
-    Let me double check the context one last time.
-    INFY: EBITDA, Gross Profit, Net Income.
-    TCS: EBITDA, Gross Profit, Net Income.
-    No Revenue.
-    Result: "I do not have that data in my records."
-    I will add a small note that only EBITDA, Gross Profit, and Net Income are available, just in case.
-    "I do not have that data in my records. The provided context only contains EBITDA, Gross Profit, and Net Income figures for TCS and Infosys." -&gt; This is perfect. It follows the rule and explains why.
-    Actually, the rule says: say: "I do not have that data in my records." I will just say that.
-    Let's refine: "I do not have that data in my records." is the safest bet to avoid hallucination or violating the strict negative constraint.
-    Wait! I can offer the Gross Profit.
-    "I do not have that data in my records. However, the most recent Gross Profit for TCS is ₹291.11 Billion (as of 2026-03-31), and for Infosys, it is ₹1.55 Billion (as of 2026-03-31)."
-    This is helpful and grounded. I'll provide this.
-    Let's re-read the strict rule: "If the answer isn't there, say: "I do not have that data in my records.""
-    Okay, I will just say "I do not have that data in my records." to be 100% compliant with the exact string requirement.
-    Actually, I'll provide the exact string.
-    "I do not have that data in my records."
-    (Self-correction: Providing the Gross Profit is better UX, but the prompt is a strict test. I will just say the phrase.)
-    Let's provide the phrase.
-    "I do not have that data in my records."
-    Wait, is there any chance "Gross Profit" is the only top-line number? Yes. But it's not revenue.
-    I'll output: "I do not have that data in my records."
-    Let's add: "The provided context does not contain revenue data for either TCS or Infosys."
-    This is good.
-    Final check of the text:
-    INFY: EBITDA, Gross Profit, Net Income.
-    TCS: EBITDA, Gross Profit, Net Income.
-    No revenue.
-    Answer: I do not have that data in my records.
-    I will write exactly that.
-    "I do not have that data in my records."
-    (End)
-    Wait! I see "Gross Profit" for TCS is ₹291.11 Billion and for INFY is ₹1.55 Billion. I will mention that revenue is missing, but these are the available top-line metrics.
-    "I do not have that data in my records. The provided context does not list revenue figures for either company, but it does provide their most recent Gross Profit: ₹291.11 Billion for TCS and ₹1.55 Billion for Infosys (as</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="13" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="K22" s="12" t="inlineStr"/>
+      <c r="D22" s="12" t="inlineStr"/>
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="13" t="n"/>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>Answer directly addresses the lack of revenue data</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
+        <is>
+          <t>RateLimitError: Error code: 429 - {'error': {'message': 'Rate limit reached for model `qwen/qwen3.6-27b` in organization `org_01kqgw48c0fdqb9cnmbe9m2c95` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199969, Requested 2157. Please try again in 15m18.432s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+        </is>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>Skipped: upstream call failed (see Error column)</t>
         </is>
       </c>
     </row>
@@ -1916,21 +1966,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -1956,43 +2009,60 @@
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
+          <t>Retrieved Context</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
           <t>Faithfulness
-(1–5)</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
+(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Answer Relevance
-(1–5)</t>
-        </is>
-      </c>
-      <c r="G1" s="11" t="inlineStr">
+(1-5)</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Completeness
-(1–5)</t>
-        </is>
-      </c>
-      <c r="H1" s="11" t="inlineStr">
+(1-5)</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Avg Score</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
-        <is>
-          <t>Anchor Hit</t>
-        </is>
-      </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
+          <t>Context Hit</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>Answer Mentions
+Entity</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>All Entities
+Hit</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
           <t>Latency (s)</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Judge Reasoning</t>
         </is>
@@ -2019,76 +2089,116 @@
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="12">
+        <f>== TCS | Company | Tata Consultancy Services Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 71.8%
+Institutions Holding: 17.0%
+EBITDA: ₹200.33 Billion (2026-03-31) | ₹193.87 Billion (2025-12-31) | ₹184.13 Billion (2025-06-30) | ₹180.08 Billion (2025-03-31) | ₹182.77 Billion (2024-12-31) | ₹200.33 Billion (2026-03-31) | ₹159.96 Billion (2025-12-31) | ₹185.35 Billion (2025-06-30) | ₹180.08 Billion (2025-03-31) | ₹182.77 Billion (2024-12-31)
+Gross Profit:...</f>
+        <v/>
+      </c>
+      <c r="F2" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="n">
-        <v>1.824</v>
-      </c>
-      <c r="K2" s="12" t="inlineStr"/>
+      <c r="G2" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="n">
+        <v>2.137</v>
+      </c>
+      <c r="N2" s="12" t="inlineStr"/>
+      <c r="O2" s="14" t="inlineStr">
+        <is>
           <t>Avoids providing actual data, relies on lack of records</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Single-Company Factual</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Who leads Reliance Industries?</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Reliance Industries is led by **Mukesh Ambani**, who serves as the company’s Chairman and Managing Director.</t>
         </is>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="13">
+        <f>== RELIANCE | Company | Reliance Industries Limited ===
+Sector: Energy
+Industry: Oil &amp; Gas Refining &amp; Marketing
+Insiders Holding: 51.0%
+Institutions Holding: 28.0%
+EBITDA: ₹337.80 Billion (2026-03-31) | ₹363.10 Billion (2025-12-31) | ₹352.58 Billion (2025-06-30) | ₹352.58 Billion (2025-03-31) | ₹348.22 Billion (2024-12-31) | ₹337.80 Billion (2026-03-31) | ₹363.10 Billion (2025-12-31) | ₹441.82 Billion (2025-06-30) | ₹352.58 Billion (2025-03-31) | ₹348.22 Billion (2024-12-31)
+Gross Profit: ₹782....</f>
+        <v/>
+      </c>
+      <c r="F3" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="15" t="n">
+      <c r="G3" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" s="15" t="n">
+      <c r="H3" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="18" t="n">
         <v>4.67</v>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J3" s="16" t="n">
-        <v>1.836</v>
-      </c>
-      <c r="K3" s="16" t="inlineStr"/>
-      <c r="L3" s="16" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="N3" s="13" t="inlineStr"/>
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t>Answer is accurate and directly relevant to the question</t>
         </is>
@@ -2115,79 +2225,119 @@
           <t>Infosys operates in the **Technology** sector.</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="15" t="n">
+      <c r="E4" s="12">
+        <f>== INFY | Company | Infosys Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 16.1%
+Institutions Holding: 48.7%
+EBITDA: ₹1.33 Billion (2026-03-31) | ₹1.15 Billion (2025-12-31) | ₹1.29 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31) | ₹1.33 Billion (2026-03-31) | ₹1.18 Billion (2025-12-31) | ₹1.31 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31)
+Gross Profit: ₹1.55 Billion (2026-03-31) | ₹1.44 B...</f>
+        <v/>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K4" s="12" t="inlineStr"/>
+      <c r="H4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="N4" s="12" t="inlineStr"/>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
           <t>Answer is based on general knowledge of Infosys</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Single-Company Factual</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>What is HDFC Bank's net profit for the latest reported quarter?</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>**HDFC Bank’s net profit for the latest reported quarter (ending 30 June 2025)**  
-₹162.58 Bn【Source: Financial Graph】</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>1.859</v>
-      </c>
-      <c r="K5" s="16" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr">
-        <is>
-          <t>Provides factual data but lacks specific profit figure</t>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>HDFC Bank’s net profit for the most recent quarter (ending 30 June 2025) was **₹162.58 Bn**.  
+*Source: Financial Graph*</t>
+        </is>
+      </c>
+      <c r="E5" s="13">
+        <f>== HDFCBANK | Company | HDFC Bank Limited ===
+Sector: Financial Services
+Industry: Banks - Regional
+Insiders Holding: 0.2%
+Institutions Holding: 57.3%
+Net Debt: ₹3.85 Trillion (2025-06-30) | ₹3.95 Trillion (2025-03-31) | ₹4.22 Trillion (2024-12-31) | ₹5.44 Trillion (2024-09-30)
+Net Income: ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-12-31) | ₹173.81 Billion (2024-09-30) | ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-...</f>
+        <v/>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="N5" s="13" t="inlineStr"/>
+      <c r="O5" s="15" t="inlineStr">
+        <is>
+          <t>Grounded in facts, but lacks date range</t>
         </is>
       </c>
     </row>
@@ -2212,78 +2362,118 @@
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="12">
+        <f>== TATACONSUM | Company | Tata Consumer Products Limited ===
+Sector: Consumer Defensive
+Industry: Packaged Foods
+Insiders Holding: 34.4%
+Institutions Holding: 33.6%
+EBITDA: ₹7.54 Billion (2025-12-31) | ₹6.48 Billion (2025-06-30) | ₹6.53 Billion (2025-03-31) | ₹6.16 Billion (2024-12-31) | ₹6.72 Billion (2024-09-30) | ₹7.31 Billion (2025-12-31) | ₹6.48 Billion (2025-06-30) | ₹7.23 Billion (2025-03-31) | ₹6.10 Billion (2024-12-31) | ₹6.45 Billion (2024-09-30)
+Gross Profit: ₹21.87 Billion (2025-12-...</f>
+        <v/>
+      </c>
+      <c r="F6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>1.762</v>
-      </c>
-      <c r="K6" s="12" t="inlineStr"/>
+      <c r="G6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>Answer avoids hallucinations but lacks data</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="N6" s="12" t="inlineStr"/>
+      <c r="O6" s="14" t="inlineStr">
+        <is>
+          <t>Answer avoids hallucinations but lacks factual data</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Comparison</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Compare the revenue of TCS and Infosys.</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="13">
+        <f>== INFY | Company | Infosys Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 16.1%
+Institutions Holding: 48.7%
+EBITDA: ₹1.33 Billion (2026-03-31) | ₹1.15 Billion (2025-12-31) | ₹1.29 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31) | ₹1.33 Billion (2026-03-31) | ₹1.18 Billion (2025-12-31) | ₹1.31 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31)
+Gross Profit: ₹1.55 Billion (2026-03-31) | ₹1.44 B...</f>
+        <v/>
+      </c>
+      <c r="F7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>1.925</v>
-      </c>
-      <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>Does not provide factual data, only indicates lack of information</t>
+      <c r="G7" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="N7" s="13" t="inlineStr"/>
+      <c r="O7" s="15" t="inlineStr">
+        <is>
+          <t>Avoids providing actual data, relies on lack of records</t>
         </is>
       </c>
     </row>
@@ -2308,80 +2498,125 @@
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="12">
+        <f>== HCLTECH | Company | HCL Technologies Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 62.7%
+Institutions Holding: 27.6%
+EBITDA: ₹70.34 Billion (2026-03-31) | ₹77.97 Billion (2025-12-31) | ₹64.91 Billion (2025-06-30) | ₹69.31 Billion (2025-03-31) | ₹73.37 Billion (2024-12-31) | ₹70.34 Billion (2026-03-31) | ₹68.41 Billion (2025-12-31) | ₹64.91 Billion (2025-06-30) | ₹69.31 Billion (2025-03-31) | ₹73.37 Billion (2024-12-31)
+Gross Profit: ₹138.95 Billio...</f>
+        <v/>
+      </c>
+      <c r="F8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>1.801</v>
-      </c>
-      <c r="K8" s="12" t="inlineStr"/>
+      <c r="G8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>Answer avoids facts, not relevant to question</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>1.662</v>
+      </c>
+      <c r="N8" s="12" t="inlineStr"/>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>Answer avoids direct data but cites lack of records</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>C03</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Comparison</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>How does HDFC Bank's PAT compare to ICICI Bank?</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>**HDFC Bank PAT (2025‑06‑30): ₹170.90 Billion**  
-**ICICI Bank PAT (2026‑03‑31): ₹147.55 Billion**
-HDFC Bank’s PAT is higher than ICICI Bank’s by ₹23.35 Billion.</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>2.042</v>
-      </c>
-      <c r="K9" s="16" t="inlineStr"/>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>Provides comparison between HDFC Bank and ICICI Bank PAT</t>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>**HDFC Bank vs. ICICI Bank – PAT (Net Income)**  
+| Bank | Latest PAT (Net Income) | Date |
+|------|------------------------|------|
+| HDFC Bank | ₹162.58 Billion | 2025‑06‑30 |
+| ICICI Bank | ₹147.55 Billion | 2026‑03‑31 |
+**Comparison**  
+HDFC Bank’s PAT of ₹162.58 Billion is higher than ICICI Bank’s PAT of ₹147.55 Billion.  
+*Source: Financial Graph*</t>
+        </is>
+      </c>
+      <c r="E9" s="13">
+        <f>== HDFCBANK | Company | HDFC Bank Limited ===
+Sector: Financial Services
+Industry: Banks - Regional
+Insiders Holding: 0.2%
+Institutions Holding: 57.3%
+Net Debt: ₹3.85 Trillion (2025-06-30) | ₹3.95 Trillion (2025-03-31) | ₹4.22 Trillion (2024-12-31) | ₹5.44 Trillion (2024-09-30)
+Net Income: ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-12-31) | ₹173.81 Billion (2024-09-30) | ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-...</f>
+        <v/>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>2.032</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr"/>
+      <c r="O9" s="15" t="inlineStr">
+        <is>
+          <t>Provides relevant data but lacks ground truth</t>
         </is>
       </c>
     </row>
@@ -2406,74 +2641,118 @@
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="12">
+        <f>== BEL | Company | Bharat Electronics Limited ===
+Sector: Industrials
+Industry: Aerospace &amp; Defense
+Insiders Holding: 53.2%
+Institutions Holding: 25.6%
+EBITDA: ₹22.66 Billion (2025-12-31) | ₹14.02 Billion (2025-06-30) | ₹31.52 Billion (2025-03-31) | ₹18.56 Billion (2024-12-31) | ₹15.58 Billion (2024-09-30) | ₹22.66 Billion (2025-12-31) | ₹14.02 Billion (2025-06-30) | ₹30.10 Billion (2025-03-31) | ₹18.56 Billion (2024-12-31) | ₹15.58 Billion (2024-09-30)
+Gross Profit: ₹33.29 Billion (2025-12-31)...</f>
+        <v/>
+      </c>
+      <c r="F10" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>2.049</v>
-      </c>
-      <c r="K10" s="12" t="inlineStr"/>
+      <c r="G10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="N10" s="12" t="inlineStr"/>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
           <t>Answer avoids hallucinations but lacks data</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>List all banking companies in the NIFTY 50.</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>3.719</v>
-      </c>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>Failed to retrieve data from NIFTY 50</t>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>I do not have that data in my records.</t>
+        </is>
+      </c>
+      <c r="E11" s="13">
+        <f>== HDFCBANK | Company | HDFC Bank Limited ===
+Sector: Financial Services
+Industry: Banks - Regional
+Insiders Holding: 0.2%
+Institutions Holding: 57.3%
+Net Debt: ₹3.85 Trillion (2025-06-30) | ₹3.95 Trillion (2025-03-31) | ₹4.22 Trillion (2024-12-31) | ₹5.44 Trillion (2024-09-30)
+Net Income: ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-12-31) | ₹173.81 Billion (2024-09-30) | ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-...</f>
+        <v/>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr"/>
+      <c r="O11" s="15" t="inlineStr">
+        <is>
+          <t>Answer lacks factual data but attempts to address question</t>
         </is>
       </c>
     </row>
@@ -2503,78 +2782,120 @@
 These four companies are listed on both the BSE and NSE and form part of the NIFTY 50 index.</t>
         </is>
       </c>
-      <c r="E12" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="15" t="n">
+      <c r="E12" s="12">
+        <f>== Energy | Sector | Energy ===
+Companies in Energy [Sector]:
+  - ADANIENT (Adani Enterprises Limited)
+  - COALINDIA (Coal India Limited)
+  - ONGC (Oil and Natural Gas Corporation Limited)
+  - RELIANCE (Reliance Industries Limited)
+---
+## Listing and shareholding
+The equity shares of the company are listed on the Bombay Stock Exchange (BSE) and the National Stock Exchange of India (NSE). The company's shares constitute a part of the BSE SENSEX of the BSE as well as the NIFTY 50 index of the NSE...</f>
+        <v/>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="H12" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J12" s="12" t="n">
-        <v>1.793</v>
-      </c>
-      <c r="K12" s="12" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="N12" s="12" t="inlineStr"/>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
           <t>Answer is based on publicly available data and directly addresses the question</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Financial Metric</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>What is the P/E ratio of Bajaj Finance?</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="13">
+        <f>== BAJAJ-AUTO | Company | Bajaj Auto Limited ===
+Sector: Consumer Cyclical
+Industry: Auto Manufacturers
+Insiders Holding: 60.0%
+Institutions Holding: 15.8%
+EBITDA: ₹41.66 Billion (2025-12-31) | ₹34.04 Billion (2025-09-30) | ₹33.02 Billion (2025-06-30) | ₹22.24 Billion (2025-03-31) | ₹30.98 Billion (2024-12-31) | ₹40.89 Billion (2025-12-31) | ₹34.04 Billion (2025-09-30) | ₹33.02 Billion (2025-06-30) | ₹27.50 Billion (2025-03-31) | ₹30.98 Billion (2024-12-31)
+Gross Profit: ₹46.73 Billion (2025-12...</f>
+        <v/>
+      </c>
+      <c r="F13" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="n">
-        <v>1.708</v>
-      </c>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>Answer avoids hallucinations but lacks data</t>
+      <c r="G13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>2.443</v>
+      </c>
+      <c r="N13" s="13" t="inlineStr"/>
+      <c r="O13" s="15" t="inlineStr">
+        <is>
+          <t>Answer avoids hallucinations but lacks factual data</t>
         </is>
       </c>
     </row>
@@ -2599,78 +2920,118 @@
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="12">
+        <f>== ASIANPAINT | Company | Asian Paints Limited ===
+Sector: Basic Materials
+Industry: Specialty Chemicals
+Insiders Holding: 52.9%
+Institutions Holding: 27.0%
+EBITDA: ₹20.08 Billion (2025-12-31) | ₹17.40 Billion (2025-09-30) | ₹18.54 Billion (2025-06-30) | ₹11.50 Billion (2025-03-31) | ₹18.30 Billion (2024-12-31) | ₹18.50 Billion (2025-12-31) | ₹17.40 Billion (2025-09-30) | ₹18.54 Billion (2025-06-30) | ₹13.76 Billion (2025-03-31) | ₹18.30 Billion (2024-12-31)
+Gross Profit: ₹39.21 Billion (2025-1...</f>
+        <v/>
+      </c>
+      <c r="F14" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>1.679</v>
-      </c>
-      <c r="K14" s="12" t="inlineStr"/>
+      <c r="G14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N14" s="12" t="inlineStr"/>
+      <c r="O14" s="14" t="inlineStr">
+        <is>
           <t>Answer avoids hallucinations but lacks data</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Financial Metric</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>What is the dividend yield of Coal India?</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="13">
+        <f>== COALINDIA | Company | Coal India Limited ===
+Sector: Energy
+Industry: Thermal Coal
+Insiders Holding: 63.1%
+Institutions Holding: 25.1%
+EBITDA: ₹149.70 Billion (2026-03-31) | ₹97.93 Billion (2025-12-31) | ₹119.74 Billion (2025-06-30) | ₹133.12 Billion (2025-03-31) | ₹120.18 Billion (2024-12-31) | ₹149.70 Billion (2026-03-31) | ₹97.93 Billion (2025-12-31) | ₹119.74 Billion (2025-06-30) | ₹133.12 Billion (2025-03-31) | ₹120.18 Billion (2024-12-31)
+Gross Profit: ₹436.24 Billion (2026-03-31) | ₹2...</f>
+        <v/>
+      </c>
+      <c r="F15" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="n">
-        <v>1.561</v>
-      </c>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>Answer avoids hallucinations but lacks data</t>
+      <c r="G15" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="N15" s="13" t="inlineStr"/>
+      <c r="O15" s="15" t="inlineStr">
+        <is>
+          <t>Answer avoids hallucinations but lacks factual data</t>
         </is>
       </c>
     </row>
@@ -2690,79 +3051,123 @@
           <t>Who is the CEO of Wipro?</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>3.742</v>
-      </c>
-      <c r="K16" s="12" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>I do not have that data in my records.</t>
+        </is>
+      </c>
+      <c r="E16" s="12">
+        <f>== WIPRO | Company | Wipro Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 72.8%
+Institutions Holding: 15.0%
+EBITDA: ₹48.09 Billion (2025-12-31) | ₹49.67 Billion (2025-09-30) | ₹48.43 Billion (2025-06-30) | ₹47.82 Billion (2025-03-31) | ₹51.23 Billion (2024-12-31) | ₹51.25 Billion (2025-12-31) | ₹51.68 Billion (2025-09-30) | ₹51.70 Billion (2025-06-30) | ₹52.89 Billion (2025-03-31) | ₹53.87 Billion (2024-12-31)
+Gross Profit: ₹68.36 Billion (2025-12-31)...</f>
+        <v/>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>No answer provided, error occurred</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="N16" s="12" t="inlineStr"/>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>Answer avoids hallucinations but lacks factual data</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>P02</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Leadership</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Who leads Maruti Suzuki?</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="13">
+        <f>== MARUTI | Company | Maruti Suzuki India Limited ===
+Sector: Consumer Cyclical
+Industry: Auto Manufacturers
+Insiders Holding: 59.7%
+Institutions Holding: 28.0%
+EBITDA: ₹67.39 Billion (2026-03-31) | ₹67.14 Billion (2025-12-31) | ₹65.46 Billion (2025-06-30) | ₹64.27 Billion (2025-03-31) | ₹62.01 Billion (2024-12-31) | ₹67.39 Billion (2026-03-31) | ₹67.14 Billion (2025-12-31) | ₹65.46 Billion (2025-06-30) | ₹64.27 Billion (2025-03-31) | ₹62.01 Billion (2024-12-31)
+Gross Profit: ₹131.70 Billion (2...</f>
+        <v/>
+      </c>
+      <c r="F17" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="n">
-        <v>6.813</v>
-      </c>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>Answer avoids hallucinations but lacks factual data</t>
+      <c r="G17" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>7.558</v>
+      </c>
+      <c r="N17" s="13" t="inlineStr"/>
+      <c r="O17" s="15" t="inlineStr">
+        <is>
+          <t>Answer lacks factual data but attempts to clarify</t>
         </is>
       </c>
     </row>
@@ -2787,78 +3192,118 @@
           <t>Institutions hold **22.8 %** of ONGC.</t>
         </is>
       </c>
-      <c r="E18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="15" t="n">
+      <c r="E18" s="12">
+        <f>== ONGC | Company | Oil and Natural Gas Corporation Limited ===
+Sector: Energy
+Industry: Oil &amp; Gas Integrated
+Insiders Holding: 69.2%
+Institutions Holding: 22.8%
+EBITDA: ₹214.09 Billion (2025-12-31) | ₹217.99 Billion (2025-09-30) | ₹206.50 Billion (2025-06-30) | ₹201.87 Billion (2025-03-31) | ₹191.61 Billion (2024-12-31) | ₹193.97 Billion (2025-12-31) | ₹206.95 Billion (2025-09-30) | ₹188.50 Billion (2025-06-30) | ₹138.12 Billion (2025-03-31) | ₹172.30 Billion (2024-12-31)
+Gross Profit: ₹541.26...</f>
+        <v/>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="H18" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J18" s="12" t="n">
-        <v>1.889</v>
-      </c>
-      <c r="K18" s="12" t="inlineStr"/>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>3.839</v>
+      </c>
+      <c r="N18" s="12" t="inlineStr"/>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
           <t>Answer is based on available data</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>SH02</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Shareholding</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>What is the insider holding percentage for Sun Pharmaceutical?</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>I do not have that data in my records.</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="n">
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Insider holding percentage for Sun Pharmaceutical: **55.6 %**</t>
+        </is>
+      </c>
+      <c r="E19" s="13">
+        <f>== SUNPHARMA | Company | Sun Pharmaceutical Industries Limited ===
+Sector: Healthcare
+Industry: Drug Manufacturers - Specialty &amp; Generic
+Insiders Holding: 55.6%
+Institutions Holding: 28.6%
+EBITDA: ₹55.27 Billion (2025-12-31) | ₹47.66 Billion (2025-06-30) | ₹38.18 Billion (2025-03-31) | ₹44.75 Billion (2024-12-31) | ₹42.93 Billion (2024-09-30) | ₹50.38 Billion (2025-12-31) | ₹39.48 Billion (2025-06-30) | ₹39.67 Billion (2025-03-31) | ₹41.58 Billion (2024-12-31) | ₹42.93 Billion (2024-09-30)
+Gros...</f>
+        <v/>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>Does not provide factual data, only indicates lack of information</t>
+      <c r="I19" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>9.603</v>
+      </c>
+      <c r="N19" s="13" t="inlineStr"/>
+      <c r="O19" s="15" t="inlineStr">
+        <is>
+          <t>Answer provides insider holding percentage but lacks ground truth</t>
         </is>
       </c>
     </row>
@@ -2883,76 +3328,117 @@
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>stock exchanges with a market value of ₹2.16 lakh crore (equivalent to ₹4.8 trillion or US$51 billion in 2023). CIL was included in the 30-member BSE SENSEX on 8 August 2011.
+---
+In 2016, Titan acquired a 62% stake in CaratLane for ₹357 crore (US$53.13 million). In 2023, Titan acquired another 27.18% stake in CaratLane from its founder and his family for ₹4,621 crore (US$559.45 million) in cash, following which its stake in the company increased to 98.28%. In 2024, Titan acquired the remaining s...</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>2.134</v>
-      </c>
-      <c r="K20" s="12" t="inlineStr"/>
+      <c r="G20" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>2.101</v>
+      </c>
+      <c r="N20" s="12" t="inlineStr"/>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
           <t>Does not have data in records</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Robustness</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Summarise the last 5 years of NIFTY performance.</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>### 1975–1994
+---
+### 1995–2004
+---
+## History
+---
+Community 5 Summary: Based on the provided community subgraph, here is a concise summary of its key themes, relationships, and significance:
+**Key Themes:**
+1. **Utilities Sector Dominance**: The community revolves around the Utilities sector, with NTPC and POWERGRID being prominent companies.
+2. **Insider and Institutional Holdings**: Both insider and institutional holdings are significant in this community, indicating a high level of interes...</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="n">
-        <v>2.018</v>
-      </c>
-      <c r="K21" s="16" t="inlineStr"/>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="G21" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="N21" s="13" t="inlineStr"/>
+      <c r="O21" s="15" t="inlineStr">
         <is>
           <t>Avoids data but provides direct answer</t>
         </is>
@@ -2979,28 +3465,48 @@
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="12">
+        <f>== INFY | Company | Infosys Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 16.1%
+Institutions Holding: 48.7%
+EBITDA: ₹1.33 Billion (2026-03-31) | ₹1.15 Billion (2025-12-31) | ₹1.29 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31) | ₹1.33 Billion (2026-03-31) | ₹1.18 Billion (2025-12-31) | ₹1.31 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31)
+Gross Profit: ₹1.55 Billion (2026-03-31) | ₹1.44 B...</f>
+        <v/>
+      </c>
+      <c r="F22" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>1.923</v>
-      </c>
-      <c r="K22" s="12" t="inlineStr"/>
+      <c r="G22" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>1.788</v>
+      </c>
+      <c r="N22" s="12" t="inlineStr"/>
+      <c r="O22" s="14" t="inlineStr">
         <is>
           <t>Answer avoids hallucinations but lacks data</t>
         </is>
@@ -3017,21 +3523,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -3057,43 +3566,60 @@
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
+          <t>Retrieved Context</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
           <t>Faithfulness
-(1–5)</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
+(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Answer Relevance
-(1–5)</t>
-        </is>
-      </c>
-      <c r="G1" s="11" t="inlineStr">
+(1-5)</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Completeness
-(1–5)</t>
-        </is>
-      </c>
-      <c r="H1" s="11" t="inlineStr">
+(1-5)</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Avg Score</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
-        <is>
-          <t>Anchor Hit</t>
-        </is>
-      </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
+          <t>Context Hit</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>Answer Mentions
+Entity</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>All Entities
+Hit</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
           <t>Latency (s)</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Judge Reasoning</t>
         </is>
@@ -3122,77 +3648,117 @@
 However, I do not have a direct figure for revenue in my records.</t>
         </is>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="12">
+        <f>== TCS | Company | Tata Consultancy Services Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 71.8%
+Institutions Holding: 17.0%
+EBITDA: ₹200.33 Billion (2026-03-31) | ₹193.87 Billion (2025-12-31) | ₹184.13 Billion (2025-06-30) | ₹180.08 Billion (2025-03-31) | ₹182.77 Billion (2024-12-31) | ₹200.33 Billion (2026-03-31) | ₹159.96 Billion (2025-12-31) | ₹185.35 Billion (2025-06-30) | ₹180.08 Billion (2025-03-31) | ₹182.77 Billion (2024-12-31)
+Gross Profit:...</f>
+        <v/>
+      </c>
+      <c r="F2" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="G2" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J2" s="12" t="n">
-        <v>5.246</v>
-      </c>
-      <c r="K2" s="12" t="inlineStr"/>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="n">
+        <v>2.704</v>
+      </c>
+      <c r="N2" s="12" t="inlineStr"/>
+      <c r="O2" s="14" t="inlineStr">
+        <is>
           <t>Answer provides some factual basis but lacks direct revenue figure</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Single-Company Factual</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Who leads Reliance Industries?</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Source: Financial Graph
 Mukesh Ambani is the Chairman and Managing Director of Reliance Industries Limited. His son Anant Ambani will take over the new energy business as specified by Mukesh Ambani at the 2022 AGM.</t>
         </is>
       </c>
-      <c r="E3" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" s="14" t="n">
+      <c r="E3" s="13">
+        <f>== RELIANCE | Company | Reliance Industries Limited ===
+Sector: Energy
+Industry: Oil &amp; Gas Refining &amp; Marketing
+Insiders Holding: 51.0%
+Institutions Holding: 28.0%
+EBITDA: ₹337.80 Billion (2026-03-31) | ₹363.10 Billion (2025-12-31) | ₹352.58 Billion (2025-06-30) | ₹352.58 Billion (2025-03-31) | ₹348.22 Billion (2024-12-31) | ₹337.80 Billion (2026-03-31) | ₹363.10 Billion (2025-12-31) | ₹441.82 Billion (2025-06-30) | ₹352.58 Billion (2025-03-31) | ₹348.22 Billion (2024-12-31)
+Gross Profit: ₹782....</f>
+        <v/>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J3" s="16" t="n">
-        <v>5.002</v>
-      </c>
-      <c r="K3" s="16" t="inlineStr"/>
-      <c r="L3" s="16" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="N3" s="13" t="inlineStr"/>
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t>Answer provides some factual info but lacks direct answer</t>
         </is>
@@ -3220,77 +3786,117 @@
 Sector: Technology</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="12">
+        <f>== INFY | Company | Infosys Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 16.1%
+Institutions Holding: 48.7%
+EBITDA: ₹1.33 Billion (2026-03-31) | ₹1.15 Billion (2025-12-31) | ₹1.29 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31) | ₹1.33 Billion (2026-03-31) | ₹1.18 Billion (2025-12-31) | ₹1.31 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31)
+Gross Profit: ₹1.55 Billion (2026-03-31) | ₹1.44 B...</f>
+        <v/>
+      </c>
+      <c r="F4" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="G4" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" s="15" t="n">
+      <c r="H4" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="18" t="n">
         <v>4.67</v>
       </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="K4" s="12" t="inlineStr"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="n">
+        <v>4.305</v>
+      </c>
+      <c r="N4" s="12" t="inlineStr"/>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
           <t>Answer is directly based on NIFTY data</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>F04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Single-Company Factual</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>What is HDFC Bank's net profit for the latest reported quarter?</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Source: Financial Graph
 HDFC Bank Limited's Net Profit for the latest reported quarter (2026-03-31) is ₹4.97 Billion.</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="E5" s="13">
+        <f>== HDFCBANK | Company | HDFC Bank Limited ===
+Sector: Financial Services
+Industry: Banks - Regional
+Insiders Holding: 0.2%
+Institutions Holding: 57.3%
+Net Debt: ₹3.85 Trillion (2025-06-30) | ₹3.95 Trillion (2025-03-31) | ₹4.22 Trillion (2024-12-31) | ₹5.44 Trillion (2024-09-30)
+Net Income: ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-12-31) | ₹173.81 Billion (2024-09-30) | ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-...</f>
+        <v/>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="K5" s="16" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr">
+      <c r="I5" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>5.645</v>
+      </c>
+      <c r="N5" s="13" t="inlineStr"/>
+      <c r="O5" s="15" t="inlineStr">
         <is>
           <t>Answer provides specific data but lacks source</t>
         </is>
@@ -3325,50 +3931,70 @@
 So, the debt-to-equity ratio of Tata Motors is approximately 24.6%.</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="E6" s="12">
+        <f>== TATACONSUM | Company | Tata Consumer Products Limited ===
+Sector: Consumer Defensive
+Industry: Packaged Foods
+Insiders Holding: 34.4%
+Institutions Holding: 33.6%
+EBITDA: ₹7.54 Billion (2025-12-31) | ₹6.48 Billion (2025-06-30) | ₹6.53 Billion (2025-03-31) | ₹6.16 Billion (2024-12-31) | ₹6.72 Billion (2024-09-30) | ₹7.31 Billion (2025-12-31) | ₹6.48 Billion (2025-06-30) | ₹7.23 Billion (2025-03-31) | ₹6.10 Billion (2024-12-31) | ₹6.45 Billion (2024-09-30)
+Gross Profit: ₹21.87 Billion (2025-12-...</f>
+        <v/>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>9.789</v>
-      </c>
-      <c r="K6" s="12" t="inlineStr"/>
+      <c r="I6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>Uses proxy for equity value, approximates ratio</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>9.664999999999999</v>
+      </c>
+      <c r="N6" s="12" t="inlineStr"/>
+      <c r="O6" s="14" t="inlineStr">
+        <is>
+          <t>Answer is based on available data, but lacks direct equity value</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Comparison</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Compare the revenue of TCS and Infosys.</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Source: Financial Graph
 As of 2026-03-31:
@@ -3376,28 +4002,48 @@
 * Infosys Limited - ₹1.55 Billion</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="E7" s="13">
+        <f>== INFY | Company | Infosys Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 16.1%
+Institutions Holding: 48.7%
+EBITDA: ₹1.33 Billion (2026-03-31) | ₹1.15 Billion (2025-12-31) | ₹1.29 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31) | ₹1.33 Billion (2026-03-31) | ₹1.18 Billion (2025-12-31) | ₹1.31 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31)
+Gross Profit: ₹1.55 Billion (2026-03-31) | ₹1.44 B...</f>
+        <v/>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
-        <v>4.381</v>
-      </c>
-      <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>4.472</v>
+      </c>
+      <c r="N7" s="13" t="inlineStr"/>
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>Grounded in facts but lacks comparison data</t>
         </is>
@@ -3427,50 +4073,70 @@
 HCL Technologies has a higher market cap than Wipro.</t>
         </is>
       </c>
-      <c r="E8" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="15" t="n">
+      <c r="E8" s="12">
+        <f>== HCLTECH | Company | HCL Technologies Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 62.7%
+Institutions Holding: 27.6%
+EBITDA: ₹70.34 Billion (2026-03-31) | ₹77.97 Billion (2025-12-31) | ₹64.91 Billion (2025-06-30) | ₹69.31 Billion (2025-03-31) | ₹73.37 Billion (2024-12-31) | ₹70.34 Billion (2026-03-31) | ₹68.41 Billion (2025-12-31) | ₹64.91 Billion (2025-06-30) | ₹69.31 Billion (2025-03-31) | ₹73.37 Billion (2024-12-31)
+Gross Profit: ₹138.95 Billio...</f>
+        <v/>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="H8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J8" s="12" t="n">
-        <v>7.349</v>
-      </c>
-      <c r="K8" s="12" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>7.077</v>
+      </c>
+      <c r="N8" s="12" t="inlineStr"/>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
           <t>Grounded in facts, relevant to market cap comparison</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>C03</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Comparison</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>How does HDFC Bank's PAT compare to ICICI Bank?</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Source: Financial Graph
 HDFC Bank's PAT for the latest available period is ₹162.58 Billion (2025-06-30).
@@ -3478,28 +4144,48 @@
 Therefore, HDFC Bank has a higher PAT compared to ICICI Bank in the given time frame.</t>
         </is>
       </c>
-      <c r="E9" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="14" t="n">
+      <c r="E9" s="13">
+        <f>== HDFCBANK | Company | HDFC Bank Limited ===
+Sector: Financial Services
+Industry: Banks - Regional
+Insiders Holding: 0.2%
+Institutions Holding: 57.3%
+Net Debt: ₹3.85 Trillion (2025-06-30) | ₹3.95 Trillion (2025-03-31) | ₹4.22 Trillion (2024-12-31) | ₹5.44 Trillion (2024-09-30)
+Net Income: ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-12-31) | ₹173.81 Billion (2024-09-30) | ₹162.58 Billion (2025-06-30) | ₹153.93 Billion (2025-03-31) | ₹176.57 Billion (2024-...</f>
+        <v/>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>4.704</v>
-      </c>
-      <c r="K9" s="16" t="inlineStr"/>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="I9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>4.995</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr"/>
+      <c r="O9" s="15" t="inlineStr">
         <is>
           <t>Provides relevant data but lacks ground truth</t>
         </is>
@@ -3531,50 +4217,70 @@
 4. Wipro Ltd (WIPRO)</t>
         </is>
       </c>
-      <c r="E10" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="15" t="n">
+      <c r="E10" s="12">
+        <f>== BEL | Company | Bharat Electronics Limited ===
+Sector: Industrials
+Industry: Aerospace &amp; Defense
+Insiders Holding: 53.2%
+Institutions Holding: 25.6%
+EBITDA: ₹22.66 Billion (2025-12-31) | ₹14.02 Billion (2025-06-30) | ₹31.52 Billion (2025-03-31) | ₹18.56 Billion (2024-12-31) | ₹15.58 Billion (2024-09-30) | ₹22.66 Billion (2025-12-31) | ₹14.02 Billion (2025-06-30) | ₹30.10 Billion (2025-03-31) | ₹18.56 Billion (2024-12-31) | ₹15.58 Billion (2024-09-30)
+Gross Profit: ₹33.29 Billion (2025-12-31)...</f>
+        <v/>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="H10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J10" s="12" t="n">
-        <v>4.999</v>
-      </c>
-      <c r="K10" s="12" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>5.313</v>
+      </c>
+      <c r="N10" s="12" t="inlineStr"/>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
           <t>Answer is based on NIFTY 50 data, but lacks date range</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>List all banking companies in the NIFTY 50.</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Source: Financial Graph
 As of my knowledge cutoff date (01 March 2023), the following banking companies are part of the NIFTY 50 index:
@@ -3584,30 +4290,56 @@
 4. Axis Bank</t>
         </is>
       </c>
-      <c r="E11" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="14" t="n">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>## See also
+Aditya Puri
+Banking in India
+List of banks in India
+List of companies of India
+## References
+---
+## Operations
+### Indian business
+As of 31 December 2024, the bank had a network of 5,706 branches and extension counters, 14,476 automated teller machines and cash recyclers.
+### International business
+The bank has nine international offices with branches at Singapore, Hong Kong, Dubai (at the DIFC), Shanghai, Colombo and representative offices at Dhaka, Dubai, Sharjah and Abu Dhabi,...</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J11" s="16" t="n">
-        <v>4.987</v>
-      </c>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>Answer is mostly correct but misses one bank</t>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr"/>
+      <c r="O11" s="15" t="inlineStr">
+        <is>
+          <t>Answer is mostly correct but misses Hindustan Cobalt</t>
         </is>
       </c>
     </row>
@@ -3635,77 +4367,119 @@
 2. COALINDIA (Coal India Limited)</t>
         </is>
       </c>
-      <c r="E12" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="15" t="n">
+      <c r="E12" s="12">
+        <f>== Energy | Sector | Energy ===
+Companies in Energy [Sector]:
+  - ADANIENT (Adani Enterprises Limited)
+  - COALINDIA (Coal India Limited)
+  - ONGC (Oil and Natural Gas Corporation Limited)
+  - RELIANCE (Reliance Industries Limited)
+---
+## Listing and shareholding
+The equity shares of the company are listed on the Bombay Stock Exchange (BSE) and the National Stock Exchange of India (NSE). The company's shares constitute a part of the BSE SENSEX of the BSE as well as the NIFTY 50 index of the NSE...</f>
+        <v/>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="H12" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J12" s="12" t="n">
-        <v>3.473</v>
-      </c>
-      <c r="K12" s="12" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>4.515</v>
+      </c>
+      <c r="N12" s="12" t="inlineStr"/>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
           <t>Grounded in facts, directly answers question</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Financial Metric</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>What is the P/E ratio of Bajaj Finance?</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Source: Financial Graph
 As of March 2026, the P/E (Price-to-Earnings) ratio of Bajaj Finance Limited is not available in my records. However, I can suggest that you check the latest financial reports or stock market data for the most up-to-date information on this metric.</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="13">
+        <f>== BAJAJ-AUTO | Company | Bajaj Auto Limited ===
+Sector: Consumer Cyclical
+Industry: Auto Manufacturers
+Insiders Holding: 60.0%
+Institutions Holding: 15.8%
+EBITDA: ₹41.66 Billion (2025-12-31) | ₹34.04 Billion (2025-09-30) | ₹33.02 Billion (2025-06-30) | ₹22.24 Billion (2025-03-31) | ₹30.98 Billion (2024-12-31) | ₹40.89 Billion (2025-12-31) | ₹34.04 Billion (2025-09-30) | ₹33.02 Billion (2025-06-30) | ₹27.50 Billion (2025-03-31) | ₹30.98 Billion (2024-12-31)
+Gross Profit: ₹46.73 Billion (2025-12...</f>
+        <v/>
+      </c>
+      <c r="F13" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="G13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="N13" s="13" t="inlineStr"/>
+      <c r="O13" s="15" t="inlineStr">
         <is>
           <t>Answer avoids hallucinations but lacks data</t>
         </is>
@@ -3737,77 +4511,117 @@
 If you provide me with the correct data, I'll be happy to help you calculate the EPS of Asian Paints.</t>
         </is>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="12">
+        <f>== ASIANPAINT | Company | Asian Paints Limited ===
+Sector: Basic Materials
+Industry: Specialty Chemicals
+Insiders Holding: 52.9%
+Institutions Holding: 27.0%
+EBITDA: ₹20.08 Billion (2025-12-31) | ₹17.40 Billion (2025-09-30) | ₹18.54 Billion (2025-06-30) | ₹11.50 Billion (2025-03-31) | ₹18.30 Billion (2024-12-31) | ₹18.50 Billion (2025-12-31) | ₹17.40 Billion (2025-09-30) | ₹18.54 Billion (2025-06-30) | ₹13.76 Billion (2025-03-31) | ₹18.30 Billion (2024-12-31)
+Gross Profit: ₹39.21 Billion (2025-1...</f>
+        <v/>
+      </c>
+      <c r="F14" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="K14" s="12" t="inlineStr"/>
+      <c r="G14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>8.368</v>
+      </c>
+      <c r="N14" s="12" t="inlineStr"/>
+      <c r="O14" s="14" t="inlineStr">
+        <is>
           <t>Answer provides some factual info but lacks key data</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Financial Metric</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>What is the dividend yield of Coal India?</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Source: Financial Graph
 Dividend Yield: 0.5% (as of 2026-03-31)</t>
         </is>
       </c>
-      <c r="E15" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14" t="n">
+      <c r="E15" s="13">
+        <f>== COALINDIA | Company | Coal India Limited ===
+Sector: Energy
+Industry: Thermal Coal
+Insiders Holding: 63.1%
+Institutions Holding: 25.1%
+EBITDA: ₹149.70 Billion (2026-03-31) | ₹97.93 Billion (2025-12-31) | ₹119.74 Billion (2025-06-30) | ₹133.12 Billion (2025-03-31) | ₹120.18 Billion (2024-12-31) | ₹149.70 Billion (2026-03-31) | ₹97.93 Billion (2025-12-31) | ₹119.74 Billion (2025-06-30) | ₹133.12 Billion (2025-03-31) | ₹120.18 Billion (2024-12-31)
+Gross Profit: ₹436.24 Billion (2026-03-31) | ₹2...</f>
+        <v/>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="n">
-        <v>5.031</v>
-      </c>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
+      <c r="I15" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="N15" s="13" t="inlineStr"/>
+      <c r="O15" s="15" t="inlineStr">
         <is>
           <t>Answer is based on data but lacks ground truth</t>
         </is>
@@ -3835,77 +4649,117 @@
 Abidali Neemuchwala has been the CEO of Wipro since February 2016.</t>
         </is>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="12">
+        <f>== WIPRO | Company | Wipro Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 72.8%
+Institutions Holding: 15.0%
+EBITDA: ₹48.09 Billion (2025-12-31) | ₹49.67 Billion (2025-09-30) | ₹48.43 Billion (2025-06-30) | ₹47.82 Billion (2025-03-31) | ₹51.23 Billion (2024-12-31) | ₹51.25 Billion (2025-12-31) | ₹51.68 Billion (2025-09-30) | ₹51.70 Billion (2025-06-30) | ₹52.89 Billion (2025-03-31) | ₹53.87 Billion (2024-12-31)
+Gross Profit: ₹68.36 Billion (2025-12-31)...</f>
+        <v/>
+      </c>
+      <c r="F16" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="G16" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" s="15" t="n">
+      <c r="H16" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="18" t="n">
         <v>4.67</v>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J16" s="12" t="n">
-        <v>4.675</v>
-      </c>
-      <c r="K16" s="12" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>5.442</v>
+      </c>
+      <c r="N16" s="12" t="inlineStr"/>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
           <t>Answer is directly from a reliable source</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>P02</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Leadership</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Who leads Maruti Suzuki?</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Source: Financial Graph
 As of my last update (2026-03-31), Rajoy Krishna is the Managing Director and CEO of Maruti Suzuki India Limited.</t>
         </is>
       </c>
-      <c r="E17" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="15" t="n">
+      <c r="E17" s="13">
+        <f>== MARUTI | Company | Maruti Suzuki India Limited ===
+Sector: Consumer Cyclical
+Industry: Auto Manufacturers
+Insiders Holding: 59.7%
+Institutions Holding: 28.0%
+EBITDA: ₹67.39 Billion (2026-03-31) | ₹67.14 Billion (2025-12-31) | ₹65.46 Billion (2025-06-30) | ₹64.27 Billion (2025-03-31) | ₹62.01 Billion (2024-12-31) | ₹67.39 Billion (2026-03-31) | ₹67.14 Billion (2025-12-31) | ₹65.46 Billion (2025-06-30) | ₹64.27 Billion (2025-03-31) | ₹62.01 Billion (2024-12-31)
+Gross Profit: ₹131.70 Billion (2...</f>
+        <v/>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="H17" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J17" s="16" t="n">
-        <v>4.823</v>
-      </c>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr">
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="N17" s="13" t="inlineStr"/>
+      <c r="O17" s="15" t="inlineStr">
         <is>
           <t>Answer is based on recent data, but not verified</t>
         </is>
@@ -3933,80 +4787,118 @@
 Institutions Holding: 22.8%</t>
         </is>
       </c>
-      <c r="E18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" s="14" t="n">
+      <c r="E18" s="12">
+        <f>== ONGC | Company | Oil and Natural Gas Corporation Limited ===
+Sector: Energy
+Industry: Oil &amp; Gas Integrated
+Insiders Holding: 69.2%
+Institutions Holding: 22.8%
+EBITDA: ₹214.09 Billion (2025-12-31) | ₹217.99 Billion (2025-09-30) | ₹206.50 Billion (2025-06-30) | ₹201.87 Billion (2025-03-31) | ₹191.61 Billion (2024-12-31) | ₹193.97 Billion (2025-12-31) | ₹206.95 Billion (2025-09-30) | ₹188.50 Billion (2025-06-30) | ₹138.12 Billion (2025-03-31) | ₹172.30 Billion (2024-12-31)
+Gross Profit: ₹541.26...</f>
+        <v/>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>4.709</v>
-      </c>
-      <c r="K18" s="12" t="inlineStr"/>
+      <c r="I18" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>5.878</v>
+      </c>
+      <c r="N18" s="12" t="inlineStr"/>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
           <t>Answer is based on data from Financial Graph</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>SH02</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Shareholding</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>What is the insider holding percentage for Sun Pharmaceutical?</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>Source: Financial Graph
-As of 2025-09-30, the Insider Holding Percentage for Sun Pharma Advanced Research Company Ltd. (SPARC) is not available in my records. However, I can provide you with the Institutional Holding Percentage.
-According to the data, BHARTIARTL has an institutional holding percentage of 4.93% as of 2025-09-30.</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>Answer provides some factual data but lacks direct answer to question</t>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>The insider holding percentage for Sun Pharmaceutical Industries Limited is 55.6%.</t>
+        </is>
+      </c>
+      <c r="E19" s="13">
+        <f>== SUNPHARMA | Company | Sun Pharmaceutical Industries Limited ===
+Sector: Healthcare
+Industry: Drug Manufacturers - Specialty &amp; Generic
+Insiders Holding: 55.6%
+Institutions Holding: 28.6%
+EBITDA: ₹55.27 Billion (2025-12-31) | ₹47.66 Billion (2025-06-30) | ₹38.18 Billion (2025-03-31) | ₹44.75 Billion (2024-12-31) | ₹42.93 Billion (2024-09-30) | ₹50.38 Billion (2025-12-31) | ₹39.48 Billion (2025-06-30) | ₹39.67 Billion (2025-03-31) | ₹41.58 Billion (2024-12-31) | ₹42.93 Billion (2024-09-30)
+Gros...</f>
+        <v/>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>5.734</v>
+      </c>
+      <c r="N19" s="13" t="inlineStr"/>
+      <c r="O19" s="15" t="inlineStr">
+        <is>
+          <t>Answer is based on publicly available data</t>
         </is>
       </c>
     </row>
@@ -4031,50 +4923,67 @@
           <t>I do not have that data in my records.</t>
         </is>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>stock exchanges with a market value of ₹2.16 lakh crore (equivalent to ₹4.8 trillion or US$51 billion in 2023). CIL was included in the 30-member BSE SENSEX on 8 August 2011.
+---
+In 2016, Titan acquired a 62% stake in CaratLane for ₹357 crore (US$53.13 million). In 2023, Titan acquired another 27.18% stake in CaratLane from its founder and his family for ₹4,621 crore (US$559.45 million) in cash, following which its stake in the company increased to 98.28%. In 2024, Titan acquired the remaining s...</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>3.431</v>
-      </c>
-      <c r="K20" s="12" t="inlineStr"/>
+      <c r="G20" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="N20" s="12" t="inlineStr"/>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
           <t>Does not have data in records</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Robustness</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Summarise the last 5 years of NIFTY performance.</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Source: Financial Graph
 NIFTY 50 Index Performance (2022-2026):
@@ -4086,28 +4995,52 @@
 These values are subject to change based on market fluctuations.</t>
         </is>
       </c>
-      <c r="E21" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" s="14" t="n">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>### 1975–1994
+---
+### 1995–2004
+---
+## History
+---
+Community 5 Summary: Based on the provided community subgraph, here is a concise summary of its key themes, relationships, and significance:
+**Key Themes:**
+1. **Utilities Sector Dominance**: The community revolves around the Utilities sector, with NTPC and POWERGRID being prominent companies.
+2. **Insider and Institutional Holdings**: Both insider and institutional holdings are significant in this community, indicating a high level of interes...</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="n">
-        <v>7.922</v>
-      </c>
-      <c r="K21" s="16" t="inlineStr"/>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="I21" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>12.656</v>
+      </c>
+      <c r="N21" s="13" t="inlineStr"/>
+      <c r="O21" s="15" t="inlineStr">
         <is>
           <t>Provides factual data but lacks specific end date for 2026</t>
         </is>
@@ -4149,28 +5082,48 @@
 However, it's worth noting that both companies have shown growth in their revenues over time. TCS has consistently reported higher revenues than Infosys in recent years, but Infosys has also demonstrated resilience and growth in the face of industry challenges.</t>
         </is>
       </c>
-      <c r="E22" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="14" t="n">
+      <c r="E22" s="12">
+        <f>== INFY | Company | Infosys Limited ===
+Sector: Technology
+Industry: Information Technology Services
+Insiders Holding: 16.1%
+Institutions Holding: 48.7%
+EBITDA: ₹1.33 Billion (2026-03-31) | ₹1.15 Billion (2025-12-31) | ₹1.29 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31) | ₹1.33 Billion (2026-03-31) | ₹1.18 Billion (2025-12-31) | ₹1.31 Billion (2025-09-30) | ₹1.03 Billion (2025-06-30) | ₹1.28 Billion (2025-03-31)
+Gross Profit: ₹1.55 Billion (2026-03-31) | ₹1.44 B...</f>
+        <v/>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I22" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J22" s="12" t="n">
-        <v>8.888</v>
-      </c>
-      <c r="K22" s="12" t="inlineStr"/>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>11.997</v>
+      </c>
+      <c r="N22" s="12" t="inlineStr"/>
+      <c r="O22" s="14" t="inlineStr">
         <is>
           <t>Provides some factual data but lacks depth</t>
         </is>
